--- a/plant_doctor_recommendation_engine_template.xlsx
+++ b/plant_doctor_recommendation_engine_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marketing/PD-Product-Guide/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDBF1E2-845B-064B-A882-7A44DF22DF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C383807-E16C-C245-946B-F56559121116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36960" yWindow="500" windowWidth="34200" windowHeight="19960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5021,7 +5021,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="1:45" ht="224" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:45" ht="208" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>228</v>
       </c>
@@ -5959,7 +5959,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="32" spans="1:45" ht="224" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:45" ht="208" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>275</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="38" spans="1:44" ht="208" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:44" ht="224" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>317</v>
       </c>
@@ -6899,12 +6899,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="AJ1:AN1"/>
     <mergeCell ref="H1:O1"/>
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="U1:Z1"/>
     <mergeCell ref="AA1:AD1"/>
     <mergeCell ref="AE1:AI1"/>
-    <mergeCell ref="AJ1:AN1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
